--- a/Matching process/available_mentors.xlsx
+++ b/Matching process/available_mentors.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\LN2PEPF0000C063\EXCELCNV\be1146f6-aa99-48d4-aed1-e6ec461d7245\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hm1425_ic_ac_uk/Documents/STEMM/Term 1/UCAS mentoring testing/Matching Algorithm/Matching process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{75AF0285-2807-48FC-B2CE-03702BC62695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{581EBA5A-C403-403D-9C8D-AE855FD71D77}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{75AF0285-2807-48FC-B2CE-03702BC62695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58E558E6-1E2A-4BE5-B73C-A0A58FF58533}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{4EBA0A43-06D1-4845-94F1-4D881A7600B4}"/>
+    <workbookView xWindow="22932" yWindow="1248" windowWidth="23256" windowHeight="14616" xr2:uid="{4EBA0A43-06D1-4845-94F1-4D881A7600B4}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">in!$B$1:$E$31</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="71">
   <si>
     <t>Mentor_Email</t>
   </si>
@@ -246,13 +249,16 @@
   </si>
   <si>
     <t>hassmali0789@gmail.com</t>
+  </si>
+  <si>
+    <t>ic1225@ic.ac.uk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,6 +389,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -685,7 +699,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -728,11 +742,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -766,6 +782,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -790,9 +807,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -830,7 +847,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -936,7 +953,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1078,7 +1095,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1086,8 +1103,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{014EF4EE-CAB2-4618-B2A8-4C1649B7FAE7}">
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.42578125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1095,7 +1113,7 @@
     <col min="7" max="7" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1129,7 +1147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1146,7 +1164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1163,7 +1181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1186,7 +1204,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1209,7 +1227,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1226,7 +1244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1243,7 +1261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1260,7 +1278,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1277,7 +1295,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1300,7 +1318,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1320,7 +1338,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1337,7 +1355,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1357,7 +1375,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -1377,7 +1395,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -1400,7 +1418,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -1417,7 +1435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1443,7 +1461,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -1466,7 +1484,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1483,7 +1501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -1500,7 +1518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1520,7 +1538,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1537,7 +1555,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1554,7 +1572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1571,7 +1589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -1588,7 +1606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1608,7 +1626,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -1628,7 +1646,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -1648,7 +1666,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1668,7 +1686,37 @@
         <v>69</v>
       </c>
     </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="B1:E31" xr:uid="{014EF4EE-CAB2-4618-B2A8-4C1649B7FAE7}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Bioengineering"/>
+        <filter val="Biology"/>
+        <filter val="Chemical Engineering"/>
+        <filter val="Medical Biosciences"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="A31" r:id="rId1" xr:uid="{C5F5C3F3-C2DB-4270-B439-1362C91A238B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>